--- a/vehicle_counts.xlsx
+++ b/vehicle_counts.xlsx
@@ -490,11 +490,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -515,11 +515,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
@@ -540,11 +540,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -560,16 +560,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>bus</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -617,15 +617,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:03</t>
+          <t>2026-03-17 16:56:17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -637,11 +637,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:05</t>
+          <t>2026-03-17 16:56:18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:07</t>
+          <t>2026-03-17 16:56:20</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -677,11 +677,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:09</t>
+          <t>2026-03-17 16:56:22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -697,15 +697,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:10</t>
+          <t>2026-03-17 16:56:23</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -717,15 +717,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:11</t>
+          <t>2026-03-17 16:56:25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -737,15 +737,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:15</t>
+          <t>2026-03-17 16:56:26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>37</v>
+        <v>120</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -757,15 +757,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:17</t>
+          <t>2026-03-17 16:56:27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -777,11 +777,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:18</t>
+          <t>2026-03-17 16:56:29</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -797,15 +797,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:20</t>
+          <t>2026-03-17 16:56:31</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -817,11 +817,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:23</t>
+          <t>2026-03-17 16:56:33</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -837,15 +837,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:26</t>
+          <t>2026-03-17 16:56:35</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -857,15 +857,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:29</t>
+          <t>2026-03-17 16:56:37</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -877,11 +877,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:33</t>
+          <t>2026-03-17 16:56:39</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>271</v>
+        <v>197</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -897,11 +897,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:34</t>
+          <t>2026-03-17 16:56:41</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>293</v>
+        <v>212</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -917,15 +917,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:36</t>
+          <t>2026-03-17 16:56:41</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -937,11 +937,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:38</t>
+          <t>2026-03-17 16:56:42</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>285</v>
+        <v>220</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -957,15 +957,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-17 16:38:39</t>
+          <t>2026-03-17 16:56:45</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -977,11 +977,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-17 16:39:23</t>
+          <t>2026-03-17 16:56:46</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>414</v>
+        <v>308</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -990,18 +990,18 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Inbound</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-17 16:39:24</t>
+          <t>2026-03-17 16:56:49</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>416</v>
+        <v>274</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1009,6 +1009,926 @@
         </is>
       </c>
       <c r="D21" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:56:49</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>275</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:56:52</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>362</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:56:55</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>332</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:56:58</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>336</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:56:58</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>316</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:01</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>394</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>461</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:05</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>437</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:06</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>453</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:09</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>423</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:12</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>493</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:15</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>499</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:17</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>580</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:19</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>562</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:20</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>596</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:24</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>606</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:26</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>601</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:33</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>698</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:36</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>736</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:40</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>727</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:44</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>810</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>motorcycle</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:47</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>862</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>motorcycle</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:47</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>991</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>motorcycle</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:49</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1046</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:52</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:52</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1049</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:52</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1074</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:55</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1203</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:56</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1117</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:56</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1178</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:58</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>bus</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:57:59</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1152</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:00</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1199</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:01</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1135</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:02</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1257</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:04</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1289</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1327</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:05</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1409</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:08</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1438</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:08</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:13</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1587</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:15</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1608</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:16</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1560</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>truck</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:16</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1612</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:16</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1662</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:58:18</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1583</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>

--- a/vehicle_counts.xlsx
+++ b/vehicle_counts.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -490,11 +490,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4">
@@ -540,36 +540,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Line 1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Line 1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Inbound</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>bus</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -583,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -617,15 +592,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:17</t>
+          <t>2026-03-29 10:30:35</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -637,15 +612,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:18</t>
+          <t>2026-03-29 10:30:35</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>138</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -657,15 +632,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:20</t>
+          <t>2026-03-29 10:30:36</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -677,15 +652,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:22</t>
+          <t>2026-03-29 10:30:36</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -697,15 +672,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:23</t>
+          <t>2026-03-29 10:30:37</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -717,15 +692,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:25</t>
+          <t>2026-03-29 10:30:39</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>64</v>
+        <v>140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -737,15 +712,15 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:26</t>
+          <t>2026-03-29 10:30:40</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -757,15 +732,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:27</t>
+          <t>2026-03-29 10:30:40</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -777,11 +752,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:29</t>
+          <t>2026-03-29 10:30:41</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -797,15 +772,15 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:31</t>
+          <t>2026-03-29 10:30:41</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>114</v>
+        <v>263</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -817,11 +792,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:33</t>
+          <t>2026-03-29 10:30:42</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>129</v>
+        <v>248</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -837,15 +812,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:35</t>
+          <t>2026-03-29 10:30:44</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -857,15 +832,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:37</t>
+          <t>2026-03-29 10:30:46</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -877,15 +852,15 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:39</t>
+          <t>2026-03-29 10:30:49</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>197</v>
+        <v>327</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -897,11 +872,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:41</t>
+          <t>2026-03-29 10:30:51</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>212</v>
+        <v>464</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -917,15 +892,15 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:41</t>
+          <t>2026-03-29 10:30:51</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>263</v>
+        <v>312</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -937,11 +912,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:42</t>
+          <t>2026-03-29 10:30:52</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>220</v>
+        <v>371</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -957,15 +932,15 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:45</t>
+          <t>2026-03-29 10:30:53</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>282</v>
+        <v>384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -977,11 +952,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:46</t>
+          <t>2026-03-29 10:30:55</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>308</v>
+        <v>513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -997,15 +972,15 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:49</t>
+          <t>2026-03-29 10:30:55</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>274</v>
+        <v>550</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>motorcycle</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1017,11 +992,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:49</t>
+          <t>2026-03-29 10:30:56</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>275</v>
+        <v>469</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1037,15 +1012,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:52</t>
+          <t>2026-03-29 10:30:56</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>362</v>
+        <v>429</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1057,15 +1032,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:55</t>
+          <t>2026-03-29 10:30:57</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>332</v>
+        <v>537</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1077,11 +1052,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:58</t>
+          <t>2026-03-29 10:30:58</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>336</v>
+        <v>598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1097,11 +1072,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-17 16:56:58</t>
+          <t>2026-03-29 10:31:00</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>316</v>
+        <v>605</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1117,15 +1092,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:01</t>
+          <t>2026-03-29 10:31:00</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>394</v>
+        <v>582</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1137,11 +1112,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:03</t>
+          <t>2026-03-29 10:31:02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>461</v>
+        <v>692</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1157,11 +1132,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:05</t>
+          <t>2026-03-29 10:31:03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>437</v>
+        <v>672</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1177,11 +1152,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:06</t>
+          <t>2026-03-29 10:31:04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>453</v>
+        <v>653</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1197,15 +1172,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:09</t>
+          <t>2026-03-29 10:31:05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>423</v>
+        <v>635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1217,11 +1192,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:12</t>
+          <t>2026-03-29 10:31:06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>493</v>
+        <v>723</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1237,11 +1212,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:15</t>
+          <t>2026-03-29 10:31:08</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>499</v>
+        <v>772</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1257,15 +1232,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:17</t>
+          <t>2026-03-29 10:31:09</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>580</v>
+        <v>746</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1277,15 +1252,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:19</t>
+          <t>2026-03-29 10:31:09</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>562</v>
+        <v>768</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1297,11 +1272,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:20</t>
+          <t>2026-03-29 10:31:10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>596</v>
+        <v>797</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1317,15 +1292,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:24</t>
+          <t>2026-03-29 10:31:12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>606</v>
+        <v>841</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1337,11 +1312,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:26</t>
+          <t>2026-03-29 10:31:12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>601</v>
+        <v>774</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1357,11 +1332,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:33</t>
+          <t>2026-03-29 10:31:13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>698</v>
+        <v>824</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1377,15 +1352,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:36</t>
+          <t>2026-03-29 10:31:14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>736</v>
+        <v>942</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1397,11 +1372,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:40</t>
+          <t>2026-03-29 10:31:14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>727</v>
+        <v>904</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1417,15 +1392,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:44</t>
+          <t>2026-03-29 10:31:17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>810</v>
+        <v>925</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1437,15 +1412,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:47</t>
+          <t>2026-03-29 10:31:18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1457,15 +1432,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:47</t>
+          <t>2026-03-29 10:31:20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>motorcycle</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1477,11 +1452,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:49</t>
+          <t>2026-03-29 10:31:22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1046</v>
+        <v>967</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1497,15 +1472,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:52</t>
+          <t>2026-03-29 10:31:22</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1080</v>
+        <v>1072</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>car</t>
+          <t>truck</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1517,11 +1492,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:52</t>
+          <t>2026-03-29 10:31:23</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1537,11 +1512,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:52</t>
+          <t>2026-03-29 10:31:26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1074</v>
+        <v>1061</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1557,11 +1532,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:55</t>
+          <t>2026-03-29 10:31:28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1203</v>
+        <v>1125</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1577,11 +1552,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:56</t>
+          <t>2026-03-29 10:31:28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1597,15 +1572,15 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:56</t>
+          <t>2026-03-29 10:31:29</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1178</v>
+        <v>1076</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1617,15 +1592,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:58</t>
+          <t>2026-03-29 10:31:30</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1287</v>
+        <v>1179</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>bus</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1637,11 +1612,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-03-17 16:57:59</t>
+          <t>2026-03-29 10:31:31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1152</v>
+        <v>1132</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1657,11 +1632,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:00</t>
+          <t>2026-03-29 10:31:32</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1199</v>
+        <v>1171</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1677,15 +1652,15 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:01</t>
+          <t>2026-03-29 10:31:34</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1135</v>
+        <v>1217</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1697,11 +1672,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:02</t>
+          <t>2026-03-29 10:31:34</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1257</v>
+        <v>1180</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1717,11 +1692,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:04</t>
+          <t>2026-03-29 10:31:40</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1289</v>
+        <v>1271</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1737,11 +1712,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:05</t>
+          <t>2026-03-29 10:31:40</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1327</v>
+        <v>1312</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1757,15 +1732,15 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:05</t>
+          <t>2026-03-29 10:31:49</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1409</v>
+        <v>1395</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1777,11 +1752,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:08</t>
+          <t>2026-03-29 10:31:50</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1438</v>
+        <v>1401</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1797,11 +1772,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:08</t>
+          <t>2026-03-29 10:31:57</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1360</v>
+        <v>1455</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1817,11 +1792,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:13</t>
+          <t>2026-03-29 10:32:00</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1587</v>
+        <v>1493</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1837,11 +1812,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:15</t>
+          <t>2026-03-29 10:32:07</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1608</v>
+        <v>1523</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1857,15 +1832,15 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:16</t>
+          <t>2026-03-29 10:32:09</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1560</v>
+        <v>1555</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>truck</t>
+          <t>car</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1877,11 +1852,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:16</t>
+          <t>2026-03-29 10:32:15</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1612</v>
+        <v>1567</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1897,11 +1872,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:16</t>
+          <t>2026-03-29 10:32:18</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1662</v>
+        <v>1573</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1917,11 +1892,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-03-17 16:58:18</t>
+          <t>2026-03-29 10:32:24</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1583</v>
+        <v>1602</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1929,6 +1904,46 @@
         </is>
       </c>
       <c r="D67" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-03-29 10:32:28</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1622</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Inbound</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-03-29 10:32:36</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1748</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>Inbound</t>
         </is>
